--- a/TEngine/Configs/GameConfig/Datas/Reward.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Reward.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857CA25C-F79E-4E87-B494-6F6BDF84EB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C03154-999D-4206-9CA8-6B94ADD6C506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="2430" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reward" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>##var</t>
   </si>
@@ -78,6 +78,10 @@
   </si>
   <si>
     <t>map,int,int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡奖励2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -232,6 +236,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -244,7 +249,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="差" xfId="1" builtinId="27"/>
@@ -522,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -539,10 +543,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="3"/>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="8"/>
+      <c r="E1" s="9"/>
       <c r="F1"/>
       <c r="G1"/>
       <c r="H1"/>
@@ -573,10 +577,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="10"/>
+      <c r="E2" s="11"/>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2"/>
@@ -609,8 +613,8 @@
       <c r="C3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3"/>
@@ -647,6 +651,20 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>10001</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="6">
+        <v>10001</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D1:E1"/>

--- a/TEngine/Configs/GameConfig/Datas/Reward.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Reward.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C03154-999D-4206-9CA8-6B94ADD6C506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C43A94-2C3B-4178-B9A0-69280A96C3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="2430" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reward" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>##var</t>
   </si>
@@ -82,6 +82,10 @@
   </si>
   <si>
     <t>关卡奖励2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡奖励3</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -526,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -665,6 +669,20 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>10002</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="6">
+        <v>10002</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D1:E1"/>
